--- a/DT_公告数据表.xlsx
+++ b/DT_公告数据表.xlsx
@@ -54,7 +54,7 @@
 2. Easier resource acquisition;  
 3. Improved ad response speed;  
 4. Fixed the issue where watching ads during combat caused game crashes;  
-5. Resolved several bugs.78987987</t>
+5. Resolved several bugs.</t>
   </si>
   <si>
     <t>版本号:V 0.1.6.4
@@ -62,7 +62,7 @@
 2.资源获得更容易；
 3.提升广告响应速度;
 4.修复战斗中观看广告，导致游戏卡死的问题;
-5.修复若干Bug。7978978797897</t>
+5.修复若干Bug。</t>
   </si>
   <si>
     <t>バージョン:V 0.1.6.4

--- a/DT_公告数据表.xlsx
+++ b/DT_公告数据表.xlsx
@@ -67,28 +67,28 @@
     <t xml:space="preserve">详情韩文</t>
   </si>
   <si>
-    <t xml:space="preserve">Version: V 0.1.6.9
-v 0.1.6.8 has a critical bug that causes the game to crash. We are very sorry for affecting your experience. Please update to the latest version to enjoy the full game.
-To compensate you, after updating the game, you will receive a large amount of Gold and Diamonds to make up for the trouble caused to you.
-Thank you again for your support!</t>
-  </si>
-  <si>
-    <t xml:space="preserve">版本号:V 0.1.6.9
-v 0.1.6.8版本出现重大Bug，导致游戏崩溃，非常抱歉影响您的体验，请更新到最新版本，体验完整游戏。
-为了补偿您，更新完游戏以后，您将领取到大量的金币和钻石，来弥补对您的困扰。
-再次感谢您的支持！</t>
-  </si>
-  <si>
-    <t xml:space="preserve">バージョン:V 0.1.6.9
-v 0.1.6.8バージョンで重大なバグが発生し, ゲームがクラッシュしました. 体験に影響を与え, 大変申し訳ございません. 最新バージョンに更新して, 完全なゲームをお楽しみください.
-償として, ゲーム更新後に, 大量のゴールドとダイヤを受け取れます. ご迷惑をおかけしたお詫びです.
-改めて, ご支援に感謝いたします!</t>
-  </si>
-  <si>
-    <t xml:space="preserve">버전:V 0.1.6.9
-v 0.1.6.8 버전에서 중대한 버그가 발생하여 게임이 충돌했습니다. 체험에 영향을 주어 매우 죄송합니다. 최신 버전으로 업데이트하여 완전한 게임을 즐겨 주세요.
-보상으로, 게임 업데이트 후, 대량의 골드와 다이아를 받으실 수 있습니다. 불편을 끼친 점을 보상해 드립니다.
-다시 한 번 지원에 감사드립니다!</t>
+    <t xml:space="preserve">Version: V 0.1.7.0
+1.Improve game stability;
+2.Add support for Android 8.0, Android 9.0:
+3.Fix bugs.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">版本号:V 0.1.7.0
+1.提高游戏的稳定性；
+2.增加对安卓8.0、安卓9.0的支持：
+3.修复Bug。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">バージョン:V 0.1.7.0
+1.ゲームの安定性を向上;
+2.Android 8.0, Android 9.0のサポートを追加:
+3.バグを修正.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">버전:V 0.1.7.0
+1.게임 안정성 향상;
+2.안드로이드 8.0, 안드로이드 9.0 지원 추가:
+3.버그 수정.</t>
   </si>
 </sst>
 </file>
@@ -152,8 +152,11 @@
   <cellStyleXfs count="1">
     <xf applyAlignment="true" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="0" fillId="0" fontId="0" numFmtId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf applyAlignment="true" applyBorder="false" applyFill="false" applyFont="true" applyNumberFormat="false" applyProtection="false" borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf applyAlignment="true" applyBorder="false" applyFill="false" applyFont="true" applyNumberFormat="false" applyProtection="false" borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0">
@@ -513,7 +516,7 @@
       <c r="B2" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="3" t="s">
         <v>7</v>
       </c>
       <c r="D2" s="2" t="s">
